--- a/files/STable-4.xlsx
+++ b/files/STable-4.xlsx
@@ -22,9 +22,6 @@
     <t>Cluster</t>
   </si>
   <si>
-    <t>checks</t>
-  </si>
-  <si>
     <t>1001</t>
   </si>
   <si>
@@ -254,6 +251,9 @@
   </si>
   <si>
     <t>1093</t>
+  </si>
+  <si>
+    <t>1094</t>
   </si>
 </sst>
 </file>
@@ -620,7 +620,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -628,7 +628,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -660,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -692,7 +692,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -716,7 +716,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -724,7 +724,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -732,7 +732,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -748,7 +748,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -756,7 +756,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -812,7 +812,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -836,7 +836,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -844,7 +844,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -852,7 +852,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -876,7 +876,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -908,7 +908,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -924,7 +924,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -932,7 +932,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -972,7 +972,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -988,7 +988,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -996,7 +996,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1004,7 +1004,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1012,7 +1012,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1020,7 +1020,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1028,7 +1028,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1044,7 +1044,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1052,7 +1052,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1068,7 +1068,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1076,7 +1076,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1084,7 +1084,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1140,7 +1140,7 @@
         <v>68</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1148,7 +1148,7 @@
         <v>69</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1164,7 +1164,7 @@
         <v>71</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1188,7 +1188,7 @@
         <v>74</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1196,7 +1196,7 @@
         <v>75</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1220,7 +1220,7 @@
         <v>78</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2">
